--- a/Assignment_rules.xlsx
+++ b/Assignment_rules.xlsx
@@ -1,41 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://partner-integrations.egnyte.com/msoffice/wopi/files/ac979c5e-8e32-49e1-9025-d21bf2f2590d/WOPIServiceId_TP_EGNYTE_PLUS/WOPIUserId_-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{29D3DCEF-A42D-4A4E-9630-CE84D3F0771F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA705156-663B-4CF2-B5A7-D1CCE31CE693}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{29D3DCEF-A42D-4A4E-9630-CE84D3F0771F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FB8DC33-C9CB-4956-906A-EDEE679AF011}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{53BA1278-635B-4DEC-915C-F91C16F4A71B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{53BA1278-635B-4DEC-915C-F91C16F4A71B}"/>
   </bookViews>
   <sheets>
     <sheet name="Assignment_Rules" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="DV_BU_Filtered">_xlfn.ANCHORARRAY([1]Data_Validation_Source!$BB$2)</definedName>
-    <definedName name="DV_BU_Filtered_Defaults">_xlfn.ANCHORARRAY('[1]Set Defaults'!$H$2)</definedName>
-    <definedName name="DV_Entity_All">_xlfn.ANCHORARRAY([1]Data_Validation_Source!$BC$2)</definedName>
-    <definedName name="DV_Request_type_All">_xlfn.ANCHORARRAY([1]Data_Validation_Source!$BI$2)</definedName>
-    <definedName name="DV_Valid_ItemTypes">_xlfn.ANCHORARRAY([1]Data_Validation_Source!$BJ$2)</definedName>
-    <definedName name="DV_Valid_Priority">_xlfn.ANCHORARRAY([1]Data_Validation_Source!$BK$2)</definedName>
-    <definedName name="R_bu">[1]!Q_BU[Business unit]</definedName>
-    <definedName name="R_Buyer_name">[1]!Q_Buyer[DisplayName]</definedName>
-    <definedName name="R_entity">[1]!Q_Entity[Entity]</definedName>
-    <definedName name="R_item_type">[1]!Q_Item_type[Item type]</definedName>
-    <definedName name="R_location">[1]!Q_Location[Location]</definedName>
-    <definedName name="R_Priority">[1]!Q_Priority[Priority]</definedName>
-    <definedName name="R_projects">[1]!Q_Projects[ProjectID_Name]</definedName>
-    <definedName name="R_request_type">[1]!Q_Request_type[Request type]</definedName>
-    <definedName name="R_requester_name">[1]!Q_Requester[DisplayName]</definedName>
-    <definedName name="R_Unit">[1]!Q_Unit[Unit]</definedName>
-    <definedName name="R_warehouse_rep_name">[1]!Q_Warehouse_Rep[DisplayName]</definedName>
+    <definedName name="DV_BU_Filtered">_xlfn.ANCHORARRAY(#REF!)</definedName>
+    <definedName name="DV_BU_Filtered_Defaults">_xlfn.ANCHORARRAY(#REF!)</definedName>
+    <definedName name="DV_Entity_All">_xlfn.ANCHORARRAY(#REF!)</definedName>
+    <definedName name="DV_Request_type_All">_xlfn.ANCHORARRAY(#REF!)</definedName>
+    <definedName name="DV_Valid_ItemTypes">_xlfn.ANCHORARRAY(#REF!)</definedName>
+    <definedName name="DV_Valid_Priority">_xlfn.ANCHORARRAY(#REF!)</definedName>
+    <definedName name="R_bu">#REF!</definedName>
+    <definedName name="R_Buyer_name">#REF!</definedName>
+    <definedName name="R_entity">#REF!</definedName>
+    <definedName name="R_item_type">#REF!</definedName>
+    <definedName name="R_location">#REF!</definedName>
+    <definedName name="R_Priority">#REF!</definedName>
+    <definedName name="R_projects">#REF!</definedName>
+    <definedName name="R_request_type">#REF!</definedName>
+    <definedName name="R_requester_name">#REF!</definedName>
+    <definedName name="R_Unit">#REF!</definedName>
+    <definedName name="R_warehouse_rep_name">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="44">
   <si>
     <t>Entity</t>
   </si>
@@ -123,9 +120,6 @@
     <t>Material | General</t>
   </si>
   <si>
-    <t>Service | TPI &amp; Training services</t>
-  </si>
-  <si>
     <t>Not applicable</t>
   </si>
   <si>
@@ -185,6 +179,15 @@
   <si>
     <t>BU 220</t>
   </si>
+  <si>
+    <t>Service | TPI, Training &amp; Medical services</t>
+  </si>
+  <si>
+    <t>Nidhinraj Kariyattil</t>
+  </si>
+  <si>
+    <t>Jerry Girinivas</t>
+  </si>
 </sst>
 </file>
 
@@ -219,18 +222,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -260,64 +255,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="New request form"/>
-      <sheetName val="Set Defaults"/>
-      <sheetName val="Assignment_Rules"/>
-      <sheetName val="Request Header"/>
-      <sheetName val="Header map"/>
-      <sheetName val="Sheet3"/>
-      <sheetName val="Q_DataValidation_Source_Master"/>
-      <sheetName val="Q_DataValidation_Cache"/>
-      <sheetName val="Data_Validation_Source"/>
-      <sheetName val="App_Version"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="H2" t="str">
-            <v>BU 135</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8">
-        <row r="2">
-          <cell r="BB2" t="str">
-            <v>BU 135</v>
-          </cell>
-          <cell r="BC2" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="BI2" t="str">
-            <v>Actual Purchase</v>
-          </cell>
-          <cell r="BJ2" t="str">
-            <v>Material | General</v>
-          </cell>
-          <cell r="BK2" t="str">
-            <v>Breakdown</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="9"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
 <FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
   <bag type="Checkbox"/>
@@ -326,11 +263,6 @@
   </bag>
   <bag type="XFComplement">
     <bagId k="XFControls">1</bagId>
-  </bag>
-  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
-    <a k="MappedFeaturePropertyBags">
-      <bagId>2</bagId>
-    </a>
   </bag>
   <bag type="DXFComplements" extRef="DXFComplementsMapperExtRef">
     <a k="MappedFeaturePropertyBags">
@@ -341,8 +273,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61A2091F-4DF5-46D6-B37B-00EB866ADD41}" name="T_Assignment_Rules" displayName="T_Assignment_Rules" ref="A1:I201">
-  <autoFilter ref="A1:I201" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61A2091F-4DF5-46D6-B37B-00EB866ADD41}" name="T_Assignment_Rules" displayName="T_Assignment_Rules" ref="A1:I209">
+  <autoFilter ref="A1:I209" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{AB04191C-95A3-4BC8-95E1-569B6E8F2311}" name="Entity"/>
     <tableColumn id="2" xr3:uid="{4DDB0BC4-1A14-4C2B-87C1-D2EB72F04B12}" name="BU"/>
@@ -708,7 +640,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41963B9-6363-42C5-B861-2C46C87E7F92}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:I201"/>
+  <dimension ref="A1:I209"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
@@ -760,7 +692,7 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -771,7 +703,7 @@
       <c r="G2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2" t="b">
+      <c r="H2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -786,7 +718,7 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
@@ -797,7 +729,7 @@
       <c r="G3" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="2" t="b">
+      <c r="H3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -812,7 +744,7 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
@@ -823,7 +755,7 @@
       <c r="G4" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="2" t="b">
+      <c r="H4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -838,7 +770,7 @@
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>19</v>
@@ -849,7 +781,7 @@
       <c r="G5" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="2" t="b">
+      <c r="H5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -861,21 +793,21 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="2" t="b">
+      <c r="H6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -887,21 +819,21 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="2" t="b">
+        <v>15</v>
+      </c>
+      <c r="H7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -916,18 +848,18 @@
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
         <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="2" t="b">
+        <v>15</v>
+      </c>
+      <c r="H8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -942,18 +874,18 @@
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
         <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="2" t="b">
+        <v>17</v>
+      </c>
+      <c r="H9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -968,18 +900,18 @@
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="2" t="b">
+        <v>17</v>
+      </c>
+      <c r="H10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -994,18 +926,18 @@
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="2" t="b">
+        <v>15</v>
+      </c>
+      <c r="H11" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1017,21 +949,21 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E12" t="s">
         <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="2" t="b">
+        <v>15</v>
+      </c>
+      <c r="H12" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1043,21 +975,21 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G13" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="2" t="b">
+        <v>15</v>
+      </c>
+      <c r="H13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1072,18 +1004,18 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s">
         <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G14" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="2" t="b">
+      <c r="H14" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1098,18 +1030,18 @@
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G15" t="s">
         <v>17</v>
       </c>
-      <c r="H15" s="2" t="b">
+      <c r="H15" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1121,21 +1053,21 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="2" t="b">
+        <v>15</v>
+      </c>
+      <c r="H16" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1147,21 +1079,21 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G17" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="2" t="b">
+        <v>15</v>
+      </c>
+      <c r="H17" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1176,18 +1108,18 @@
         <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="2" t="b">
+        <v>15</v>
+      </c>
+      <c r="H18" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1199,21 +1131,21 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E19" t="s">
         <v>16</v>
       </c>
       <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" t="s">
         <v>22</v>
       </c>
-      <c r="G19" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="2" t="b">
+      <c r="H19" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1225,21 +1157,21 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
       </c>
       <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" t="s">
         <v>22</v>
       </c>
-      <c r="G20" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" s="2" t="b">
+      <c r="H20" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1251,21 +1183,21 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E21" t="s">
         <v>16</v>
       </c>
       <c r="F21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G21" t="s">
         <v>15</v>
       </c>
-      <c r="H21" s="2" t="b">
+      <c r="H21" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1277,21 +1209,21 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D22" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
       </c>
-      <c r="H22" s="2" t="b">
+      <c r="H22" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1303,21 +1235,21 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E23" t="s">
         <v>16</v>
       </c>
       <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" t="s">
         <v>22</v>
       </c>
-      <c r="G23" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" s="2" t="b">
+      <c r="H23" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1329,21 +1261,21 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
       </c>
       <c r="F24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" t="s">
         <v>22</v>
       </c>
-      <c r="G24" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" s="2" t="b">
+      <c r="H24" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1355,21 +1287,21 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E25" t="s">
         <v>16</v>
       </c>
       <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" t="s">
         <v>22</v>
       </c>
-      <c r="G25" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25" s="2" t="b">
+      <c r="H25" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1381,21 +1313,21 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E26" t="s">
         <v>19</v>
       </c>
       <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" t="s">
         <v>22</v>
       </c>
-      <c r="G26" t="s">
-        <v>15</v>
-      </c>
-      <c r="H26" s="2" t="b">
+      <c r="H26" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1404,7 +1336,7 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -1416,12 +1348,12 @@
         <v>13</v>
       </c>
       <c r="F27" t="s">
+        <v>28</v>
+      </c>
+      <c r="G27" t="s">
         <v>29</v>
       </c>
-      <c r="G27" t="s">
-        <v>30</v>
-      </c>
-      <c r="H27" s="2" t="b">
+      <c r="H27" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1430,7 +1362,7 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -1442,12 +1374,12 @@
         <v>16</v>
       </c>
       <c r="F28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H28" s="2" t="b">
+        <v>30</v>
+      </c>
+      <c r="H28" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1456,7 +1388,7 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -1468,12 +1400,12 @@
         <v>18</v>
       </c>
       <c r="F29" t="s">
+        <v>28</v>
+      </c>
+      <c r="G29" t="s">
         <v>29</v>
       </c>
-      <c r="G29" t="s">
-        <v>30</v>
-      </c>
-      <c r="H29" s="2" t="b">
+      <c r="H29" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1482,7 +1414,7 @@
         <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
@@ -1494,12 +1426,12 @@
         <v>19</v>
       </c>
       <c r="F30" t="s">
+        <v>28</v>
+      </c>
+      <c r="G30" t="s">
         <v>29</v>
       </c>
-      <c r="G30" t="s">
-        <v>30</v>
-      </c>
-      <c r="H30" s="2" t="b">
+      <c r="H30" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1508,7 +1440,7 @@
         <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
@@ -1520,12 +1452,12 @@
         <v>13</v>
       </c>
       <c r="F31" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" t="s">
         <v>29</v>
       </c>
-      <c r="G31" t="s">
-        <v>30</v>
-      </c>
-      <c r="H31" s="2" t="b">
+      <c r="H31" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1534,7 +1466,7 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -1546,12 +1478,12 @@
         <v>16</v>
       </c>
       <c r="F32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G32" t="s">
-        <v>31</v>
-      </c>
-      <c r="H32" s="2" t="b">
+        <v>30</v>
+      </c>
+      <c r="H32" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1560,7 +1492,7 @@
         <v>9</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
         <v>11</v>
@@ -1572,12 +1504,12 @@
         <v>18</v>
       </c>
       <c r="F33" t="s">
+        <v>28</v>
+      </c>
+      <c r="G33" t="s">
         <v>29</v>
       </c>
-      <c r="G33" t="s">
-        <v>30</v>
-      </c>
-      <c r="H33" s="2" t="b">
+      <c r="H33" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1586,7 +1518,7 @@
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
         <v>11</v>
@@ -1598,12 +1530,12 @@
         <v>19</v>
       </c>
       <c r="F34" t="s">
+        <v>28</v>
+      </c>
+      <c r="G34" t="s">
         <v>29</v>
       </c>
-      <c r="G34" t="s">
-        <v>30</v>
-      </c>
-      <c r="H34" s="2" t="b">
+      <c r="H34" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1612,24 +1544,24 @@
         <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
         <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E35" t="s">
         <v>16</v>
       </c>
       <c r="F35" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" t="s">
         <v>22</v>
       </c>
-      <c r="G35" t="s">
-        <v>31</v>
-      </c>
-      <c r="H35" s="2" t="b">
+      <c r="H35" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1638,24 +1570,24 @@
         <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E36" t="s">
         <v>19</v>
       </c>
       <c r="F36" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" t="s">
         <v>22</v>
       </c>
-      <c r="G36" t="s">
-        <v>30</v>
-      </c>
-      <c r="H36" s="2" t="b">
+      <c r="H36" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1664,24 +1596,24 @@
         <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
         <v>11</v>
       </c>
       <c r="D37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E37" t="s">
         <v>16</v>
       </c>
       <c r="F37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G37" t="s">
-        <v>31</v>
-      </c>
-      <c r="H37" s="2" t="b">
+        <v>30</v>
+      </c>
+      <c r="H37" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1690,24 +1622,24 @@
         <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
         <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H38" s="2" t="b">
+        <v>29</v>
+      </c>
+      <c r="H38" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1716,24 +1648,24 @@
         <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C39" t="s">
         <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E39" t="s">
         <v>16</v>
       </c>
       <c r="F39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G39" t="s">
-        <v>31</v>
-      </c>
-      <c r="H39" s="2" t="b">
+        <v>30</v>
+      </c>
+      <c r="H39" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1742,24 +1674,24 @@
         <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C40" t="s">
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G40" t="s">
-        <v>30</v>
-      </c>
-      <c r="H40" s="2" t="b">
+        <v>29</v>
+      </c>
+      <c r="H40" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1768,24 +1700,24 @@
         <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C41" t="s">
         <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E41" t="s">
         <v>13</v>
       </c>
       <c r="F41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G41" t="s">
-        <v>30</v>
-      </c>
-      <c r="H41" s="2" t="b">
+        <v>29</v>
+      </c>
+      <c r="H41" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1794,24 +1726,24 @@
         <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C42" t="s">
         <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E42" t="s">
         <v>16</v>
       </c>
       <c r="F42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G42" t="s">
-        <v>31</v>
-      </c>
-      <c r="H42" s="2" t="b">
+        <v>30</v>
+      </c>
+      <c r="H42" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1820,24 +1752,24 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
         <v>11</v>
       </c>
       <c r="D43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G43" t="s">
-        <v>30</v>
-      </c>
-      <c r="H43" s="2" t="b">
+        <v>29</v>
+      </c>
+      <c r="H43" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1846,10 +1778,10 @@
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D44" t="s">
         <v>12</v>
@@ -1858,12 +1790,12 @@
         <v>16</v>
       </c>
       <c r="F44" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G44" t="s">
-        <v>31</v>
-      </c>
-      <c r="H44" s="2" t="b">
+        <v>30</v>
+      </c>
+      <c r="H44" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1872,10 +1804,10 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D45" t="s">
         <v>12</v>
@@ -1884,12 +1816,12 @@
         <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G45" t="s">
-        <v>30</v>
-      </c>
-      <c r="H45" s="2" t="b">
+        <v>29</v>
+      </c>
+      <c r="H45" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1898,10 +1830,10 @@
         <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D46" t="s">
         <v>20</v>
@@ -1910,12 +1842,12 @@
         <v>16</v>
       </c>
       <c r="F46" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G46" t="s">
-        <v>31</v>
-      </c>
-      <c r="H46" s="2" t="b">
+        <v>30</v>
+      </c>
+      <c r="H46" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1924,10 +1856,10 @@
         <v>9</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D47" t="s">
         <v>20</v>
@@ -1936,12 +1868,12 @@
         <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G47" t="s">
-        <v>30</v>
-      </c>
-      <c r="H47" s="2" t="b">
+        <v>29</v>
+      </c>
+      <c r="H47" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1950,24 +1882,24 @@
         <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E48" t="s">
         <v>16</v>
       </c>
       <c r="F48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G48" t="s">
-        <v>31</v>
-      </c>
-      <c r="H48" s="2" t="b">
+        <v>30</v>
+      </c>
+      <c r="H48" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1976,24 +1908,24 @@
         <v>9</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E49" t="s">
         <v>19</v>
       </c>
       <c r="F49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G49" t="s">
-        <v>30</v>
-      </c>
-      <c r="H49" s="2" t="b">
+        <v>29</v>
+      </c>
+      <c r="H49" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2002,24 +1934,24 @@
         <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D50" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E50" t="s">
         <v>16</v>
       </c>
       <c r="F50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G50" t="s">
-        <v>31</v>
-      </c>
-      <c r="H50" s="2" t="b">
+        <v>30</v>
+      </c>
+      <c r="H50" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2028,24 +1960,24 @@
         <v>9</v>
       </c>
       <c r="B51" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E51" t="s">
         <v>19</v>
       </c>
       <c r="F51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G51" t="s">
-        <v>30</v>
-      </c>
-      <c r="H51" s="2" t="b">
+        <v>29</v>
+      </c>
+      <c r="H51" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2054,7 +1986,7 @@
         <v>9</v>
       </c>
       <c r="B52" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C52" t="s">
         <v>11</v>
@@ -2066,12 +1998,12 @@
         <v>13</v>
       </c>
       <c r="F52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G52" t="s">
         <v>29</v>
       </c>
-      <c r="G52" t="s">
-        <v>30</v>
-      </c>
-      <c r="H52" s="2" t="b">
+      <c r="H52" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2080,7 +2012,7 @@
         <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C53" t="s">
         <v>11</v>
@@ -2092,12 +2024,12 @@
         <v>16</v>
       </c>
       <c r="F53" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G53" t="s">
-        <v>31</v>
-      </c>
-      <c r="H53" s="2" t="b">
+        <v>30</v>
+      </c>
+      <c r="H53" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2106,7 +2038,7 @@
         <v>9</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C54" t="s">
         <v>11</v>
@@ -2118,12 +2050,12 @@
         <v>18</v>
       </c>
       <c r="F54" t="s">
+        <v>28</v>
+      </c>
+      <c r="G54" t="s">
         <v>29</v>
       </c>
-      <c r="G54" t="s">
-        <v>30</v>
-      </c>
-      <c r="H54" s="2" t="b">
+      <c r="H54" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2132,7 +2064,7 @@
         <v>9</v>
       </c>
       <c r="B55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C55" t="s">
         <v>11</v>
@@ -2144,12 +2076,12 @@
         <v>19</v>
       </c>
       <c r="F55" t="s">
+        <v>28</v>
+      </c>
+      <c r="G55" t="s">
         <v>29</v>
       </c>
-      <c r="G55" t="s">
-        <v>30</v>
-      </c>
-      <c r="H55" s="2" t="b">
+      <c r="H55" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2158,7 +2090,7 @@
         <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C56" t="s">
         <v>11</v>
@@ -2170,12 +2102,12 @@
         <v>13</v>
       </c>
       <c r="F56" t="s">
+        <v>28</v>
+      </c>
+      <c r="G56" t="s">
         <v>29</v>
       </c>
-      <c r="G56" t="s">
-        <v>30</v>
-      </c>
-      <c r="H56" s="2" t="b">
+      <c r="H56" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2184,7 +2116,7 @@
         <v>9</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C57" t="s">
         <v>11</v>
@@ -2196,12 +2128,12 @@
         <v>16</v>
       </c>
       <c r="F57" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G57" t="s">
-        <v>31</v>
-      </c>
-      <c r="H57" s="2" t="b">
+        <v>30</v>
+      </c>
+      <c r="H57" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2210,7 +2142,7 @@
         <v>9</v>
       </c>
       <c r="B58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C58" t="s">
         <v>11</v>
@@ -2222,12 +2154,12 @@
         <v>18</v>
       </c>
       <c r="F58" t="s">
+        <v>28</v>
+      </c>
+      <c r="G58" t="s">
         <v>29</v>
       </c>
-      <c r="G58" t="s">
-        <v>30</v>
-      </c>
-      <c r="H58" s="2" t="b">
+      <c r="H58" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2236,7 +2168,7 @@
         <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C59" t="s">
         <v>11</v>
@@ -2248,12 +2180,12 @@
         <v>19</v>
       </c>
       <c r="F59" t="s">
+        <v>28</v>
+      </c>
+      <c r="G59" t="s">
         <v>29</v>
       </c>
-      <c r="G59" t="s">
-        <v>30</v>
-      </c>
-      <c r="H59" s="2" t="b">
+      <c r="H59" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2262,24 +2194,24 @@
         <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C60" t="s">
         <v>11</v>
       </c>
       <c r="D60" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E60" t="s">
         <v>16</v>
       </c>
       <c r="F60" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G60" t="s">
-        <v>31</v>
-      </c>
-      <c r="H60" s="2" t="b">
+        <v>22</v>
+      </c>
+      <c r="H60" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2288,24 +2220,24 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C61" t="s">
         <v>11</v>
       </c>
       <c r="D61" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E61" t="s">
         <v>19</v>
       </c>
       <c r="F61" t="s">
+        <v>21</v>
+      </c>
+      <c r="G61" t="s">
         <v>22</v>
       </c>
-      <c r="G61" t="s">
-        <v>30</v>
-      </c>
-      <c r="H61" s="2" t="b">
+      <c r="H61" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2314,24 +2246,24 @@
         <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C62" t="s">
         <v>11</v>
       </c>
       <c r="D62" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E62" t="s">
         <v>16</v>
       </c>
       <c r="F62" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G62" t="s">
-        <v>31</v>
-      </c>
-      <c r="H62" s="2" t="b">
+        <v>30</v>
+      </c>
+      <c r="H62" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2340,24 +2272,24 @@
         <v>9</v>
       </c>
       <c r="B63" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C63" t="s">
         <v>11</v>
       </c>
       <c r="D63" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E63" t="s">
         <v>19</v>
       </c>
       <c r="F63" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G63" t="s">
-        <v>30</v>
-      </c>
-      <c r="H63" s="2" t="b">
+        <v>29</v>
+      </c>
+      <c r="H63" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2366,24 +2298,24 @@
         <v>9</v>
       </c>
       <c r="B64" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C64" t="s">
         <v>11</v>
       </c>
       <c r="D64" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E64" t="s">
         <v>16</v>
       </c>
       <c r="F64" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G64" t="s">
-        <v>31</v>
-      </c>
-      <c r="H64" s="2" t="b">
+        <v>30</v>
+      </c>
+      <c r="H64" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2392,24 +2324,24 @@
         <v>9</v>
       </c>
       <c r="B65" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C65" t="s">
         <v>11</v>
       </c>
       <c r="D65" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E65" t="s">
         <v>19</v>
       </c>
       <c r="F65" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G65" t="s">
-        <v>30</v>
-      </c>
-      <c r="H65" s="2" t="b">
+        <v>29</v>
+      </c>
+      <c r="H65" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2418,24 +2350,24 @@
         <v>9</v>
       </c>
       <c r="B66" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C66" t="s">
         <v>11</v>
       </c>
       <c r="D66" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E66" t="s">
         <v>13</v>
       </c>
       <c r="F66" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G66" t="s">
-        <v>30</v>
-      </c>
-      <c r="H66" s="2" t="b">
+        <v>29</v>
+      </c>
+      <c r="H66" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2444,24 +2376,24 @@
         <v>9</v>
       </c>
       <c r="B67" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
       </c>
       <c r="D67" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E67" t="s">
         <v>16</v>
       </c>
       <c r="F67" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G67" t="s">
-        <v>31</v>
-      </c>
-      <c r="H67" s="2" t="b">
+        <v>30</v>
+      </c>
+      <c r="H67" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2470,24 +2402,24 @@
         <v>9</v>
       </c>
       <c r="B68" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
       </c>
       <c r="D68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E68" t="s">
         <v>19</v>
       </c>
       <c r="F68" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G68" t="s">
-        <v>30</v>
-      </c>
-      <c r="H68" s="2" t="b">
+        <v>29</v>
+      </c>
+      <c r="H68" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2496,10 +2428,10 @@
         <v>9</v>
       </c>
       <c r="B69" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C69" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D69" t="s">
         <v>12</v>
@@ -2508,12 +2440,12 @@
         <v>16</v>
       </c>
       <c r="F69" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G69" t="s">
-        <v>31</v>
-      </c>
-      <c r="H69" s="2" t="b">
+        <v>30</v>
+      </c>
+      <c r="H69" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2522,10 +2454,10 @@
         <v>9</v>
       </c>
       <c r="B70" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C70" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D70" t="s">
         <v>12</v>
@@ -2534,12 +2466,12 @@
         <v>19</v>
       </c>
       <c r="F70" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G70" t="s">
-        <v>30</v>
-      </c>
-      <c r="H70" s="2" t="b">
+        <v>29</v>
+      </c>
+      <c r="H70" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2548,10 +2480,10 @@
         <v>9</v>
       </c>
       <c r="B71" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C71" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D71" t="s">
         <v>20</v>
@@ -2560,12 +2492,12 @@
         <v>16</v>
       </c>
       <c r="F71" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G71" t="s">
-        <v>31</v>
-      </c>
-      <c r="H71" s="2" t="b">
+        <v>30</v>
+      </c>
+      <c r="H71" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2574,10 +2506,10 @@
         <v>9</v>
       </c>
       <c r="B72" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C72" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D72" t="s">
         <v>20</v>
@@ -2586,12 +2518,12 @@
         <v>19</v>
       </c>
       <c r="F72" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G72" t="s">
-        <v>30</v>
-      </c>
-      <c r="H72" s="2" t="b">
+        <v>29</v>
+      </c>
+      <c r="H72" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2600,24 +2532,24 @@
         <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C73" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D73" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E73" t="s">
         <v>16</v>
       </c>
       <c r="F73" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G73" t="s">
-        <v>31</v>
-      </c>
-      <c r="H73" s="2" t="b">
+        <v>30</v>
+      </c>
+      <c r="H73" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2626,24 +2558,24 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C74" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D74" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E74" t="s">
         <v>19</v>
       </c>
       <c r="F74" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G74" t="s">
-        <v>30</v>
-      </c>
-      <c r="H74" s="2" t="b">
+        <v>29</v>
+      </c>
+      <c r="H74" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2652,24 +2584,24 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C75" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D75" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E75" t="s">
         <v>16</v>
       </c>
       <c r="F75" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G75" t="s">
-        <v>31</v>
-      </c>
-      <c r="H75" s="2" t="b">
+        <v>30</v>
+      </c>
+      <c r="H75" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2678,30 +2610,30 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C76" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D76" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E76" t="s">
         <v>19</v>
       </c>
       <c r="F76" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G76" t="s">
-        <v>30</v>
-      </c>
-      <c r="H76" s="2" t="b">
+        <v>29</v>
+      </c>
+      <c r="H76" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B77" t="s">
         <v>10</v>
@@ -2716,18 +2648,18 @@
         <v>13</v>
       </c>
       <c r="F77" t="s">
+        <v>33</v>
+      </c>
+      <c r="G77" t="s">
         <v>34</v>
       </c>
-      <c r="G77" t="s">
-        <v>35</v>
-      </c>
-      <c r="H77" s="2" t="b">
+      <c r="H77" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B78" t="s">
         <v>10</v>
@@ -2742,18 +2674,18 @@
         <v>16</v>
       </c>
       <c r="F78" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G78" t="s">
-        <v>36</v>
-      </c>
-      <c r="H78" s="2" t="b">
+        <v>35</v>
+      </c>
+      <c r="H78" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B79" t="s">
         <v>10</v>
@@ -2768,18 +2700,18 @@
         <v>18</v>
       </c>
       <c r="F79" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G79" t="s">
-        <v>36</v>
-      </c>
-      <c r="H79" s="2" t="b">
+        <v>35</v>
+      </c>
+      <c r="H79" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B80" t="s">
         <v>10</v>
@@ -2794,18 +2726,18 @@
         <v>19</v>
       </c>
       <c r="F80" t="s">
+        <v>33</v>
+      </c>
+      <c r="G80" t="s">
         <v>34</v>
       </c>
-      <c r="G80" t="s">
-        <v>35</v>
-      </c>
-      <c r="H80" s="2" t="b">
+      <c r="H80" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B81" t="s">
         <v>10</v>
@@ -2820,18 +2752,18 @@
         <v>13</v>
       </c>
       <c r="F81" t="s">
+        <v>33</v>
+      </c>
+      <c r="G81" t="s">
         <v>34</v>
       </c>
-      <c r="G81" t="s">
-        <v>35</v>
-      </c>
-      <c r="H81" s="2" t="b">
+      <c r="H81" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B82" t="s">
         <v>10</v>
@@ -2846,18 +2778,18 @@
         <v>16</v>
       </c>
       <c r="F82" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G82" t="s">
-        <v>36</v>
-      </c>
-      <c r="H82" s="2" t="b">
+        <v>35</v>
+      </c>
+      <c r="H82" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B83" t="s">
         <v>10</v>
@@ -2872,18 +2804,18 @@
         <v>18</v>
       </c>
       <c r="F83" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G83" t="s">
-        <v>36</v>
-      </c>
-      <c r="H83" s="2" t="b">
+        <v>35</v>
+      </c>
+      <c r="H83" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B84" t="s">
         <v>10</v>
@@ -2898,18 +2830,18 @@
         <v>19</v>
       </c>
       <c r="F84" t="s">
+        <v>33</v>
+      </c>
+      <c r="G84" t="s">
         <v>34</v>
       </c>
-      <c r="G84" t="s">
-        <v>35</v>
-      </c>
-      <c r="H84" s="2" t="b">
+      <c r="H84" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B85" t="s">
         <v>10</v>
@@ -2918,24 +2850,24 @@
         <v>11</v>
       </c>
       <c r="D85" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E85" t="s">
         <v>16</v>
       </c>
       <c r="F85" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G85" t="s">
-        <v>36</v>
-      </c>
-      <c r="H85" s="2" t="b">
+        <v>35</v>
+      </c>
+      <c r="H85" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B86" t="s">
         <v>10</v>
@@ -2944,24 +2876,24 @@
         <v>11</v>
       </c>
       <c r="D86" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E86" t="s">
         <v>19</v>
       </c>
       <c r="F86" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G86" t="s">
-        <v>35</v>
-      </c>
-      <c r="H86" s="2" t="b">
+        <v>34</v>
+      </c>
+      <c r="H86" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B87" t="s">
         <v>10</v>
@@ -2970,24 +2902,24 @@
         <v>11</v>
       </c>
       <c r="D87" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E87" t="s">
         <v>16</v>
       </c>
       <c r="F87" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G87" t="s">
-        <v>36</v>
-      </c>
-      <c r="H87" s="2" t="b">
+        <v>35</v>
+      </c>
+      <c r="H87" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B88" t="s">
         <v>10</v>
@@ -2996,24 +2928,24 @@
         <v>11</v>
       </c>
       <c r="D88" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E88" t="s">
         <v>19</v>
       </c>
       <c r="F88" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G88" t="s">
-        <v>35</v>
-      </c>
-      <c r="H88" s="2" t="b">
+        <v>34</v>
+      </c>
+      <c r="H88" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B89" t="s">
         <v>10</v>
@@ -3022,24 +2954,24 @@
         <v>11</v>
       </c>
       <c r="D89" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E89" t="s">
         <v>16</v>
       </c>
       <c r="F89" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G89" t="s">
-        <v>36</v>
-      </c>
-      <c r="H89" s="2" t="b">
+        <v>35</v>
+      </c>
+      <c r="H89" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B90" t="s">
         <v>10</v>
@@ -3048,24 +2980,24 @@
         <v>11</v>
       </c>
       <c r="D90" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E90" t="s">
         <v>19</v>
       </c>
       <c r="F90" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G90" t="s">
-        <v>35</v>
-      </c>
-      <c r="H90" s="2" t="b">
+        <v>34</v>
+      </c>
+      <c r="H90" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B91" t="s">
         <v>10</v>
@@ -3074,24 +3006,24 @@
         <v>11</v>
       </c>
       <c r="D91" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E91" t="s">
         <v>13</v>
       </c>
       <c r="F91" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G91" t="s">
-        <v>35</v>
-      </c>
-      <c r="H91" s="2" t="b">
+        <v>34</v>
+      </c>
+      <c r="H91" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B92" t="s">
         <v>10</v>
@@ -3100,24 +3032,24 @@
         <v>11</v>
       </c>
       <c r="D92" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E92" t="s">
         <v>16</v>
       </c>
       <c r="F92" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G92" t="s">
-        <v>36</v>
-      </c>
-      <c r="H92" s="2" t="b">
+        <v>35</v>
+      </c>
+      <c r="H92" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B93" t="s">
         <v>10</v>
@@ -3126,30 +3058,30 @@
         <v>11</v>
       </c>
       <c r="D93" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E93" t="s">
         <v>19</v>
       </c>
       <c r="F93" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G93" t="s">
-        <v>35</v>
-      </c>
-      <c r="H93" s="2" t="b">
+        <v>34</v>
+      </c>
+      <c r="H93" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B94" t="s">
         <v>10</v>
       </c>
       <c r="C94" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D94" t="s">
         <v>12</v>
@@ -3158,24 +3090,24 @@
         <v>16</v>
       </c>
       <c r="F94" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G94" t="s">
-        <v>36</v>
-      </c>
-      <c r="H94" s="2" t="b">
+        <v>35</v>
+      </c>
+      <c r="H94" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B95" t="s">
         <v>10</v>
       </c>
       <c r="C95" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D95" t="s">
         <v>12</v>
@@ -3184,24 +3116,24 @@
         <v>19</v>
       </c>
       <c r="F95" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G95" t="s">
-        <v>35</v>
-      </c>
-      <c r="H95" s="2" t="b">
+        <v>34</v>
+      </c>
+      <c r="H95" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B96" t="s">
         <v>10</v>
       </c>
       <c r="C96" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D96" t="s">
         <v>20</v>
@@ -3210,24 +3142,24 @@
         <v>16</v>
       </c>
       <c r="F96" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G96" t="s">
-        <v>36</v>
-      </c>
-      <c r="H96" s="2" t="b">
+        <v>35</v>
+      </c>
+      <c r="H96" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B97" t="s">
         <v>10</v>
       </c>
       <c r="C97" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D97" t="s">
         <v>20</v>
@@ -3236,122 +3168,122 @@
         <v>19</v>
       </c>
       <c r="F97" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G97" t="s">
-        <v>35</v>
-      </c>
-      <c r="H97" s="2" t="b">
+        <v>34</v>
+      </c>
+      <c r="H97" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B98" t="s">
         <v>10</v>
       </c>
       <c r="C98" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D98" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E98" t="s">
         <v>16</v>
       </c>
       <c r="F98" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G98" t="s">
-        <v>36</v>
-      </c>
-      <c r="H98" s="2" t="b">
+        <v>35</v>
+      </c>
+      <c r="H98" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B99" t="s">
         <v>10</v>
       </c>
       <c r="C99" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D99" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E99" t="s">
         <v>19</v>
       </c>
       <c r="F99" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G99" t="s">
-        <v>35</v>
-      </c>
-      <c r="H99" s="2" t="b">
+        <v>34</v>
+      </c>
+      <c r="H99" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B100" t="s">
         <v>10</v>
       </c>
       <c r="C100" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D100" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E100" t="s">
         <v>16</v>
       </c>
       <c r="F100" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G100" t="s">
-        <v>36</v>
-      </c>
-      <c r="H100" s="2" t="b">
+        <v>35</v>
+      </c>
+      <c r="H100" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B101" t="s">
         <v>10</v>
       </c>
       <c r="C101" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D101" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E101" t="s">
         <v>19</v>
       </c>
       <c r="F101" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G101" t="s">
-        <v>35</v>
-      </c>
-      <c r="H101" s="2" t="b">
+        <v>34</v>
+      </c>
+      <c r="H101" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B102" t="s">
         <v>10</v>
@@ -3365,13 +3297,19 @@
       <c r="E102" t="s">
         <v>13</v>
       </c>
-      <c r="H102" s="2" t="b">
-        <v>0</v>
+      <c r="F102" t="s">
+        <v>14</v>
+      </c>
+      <c r="G102" t="s">
+        <v>15</v>
+      </c>
+      <c r="H102" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B103" t="s">
         <v>10</v>
@@ -3385,13 +3323,19 @@
       <c r="E103" t="s">
         <v>16</v>
       </c>
-      <c r="H103" s="2" t="b">
-        <v>0</v>
+      <c r="F103" t="s">
+        <v>14</v>
+      </c>
+      <c r="G103" t="s">
+        <v>15</v>
+      </c>
+      <c r="H103" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B104" t="s">
         <v>10</v>
@@ -3405,13 +3349,19 @@
       <c r="E104" t="s">
         <v>18</v>
       </c>
-      <c r="H104" s="2" t="b">
-        <v>0</v>
+      <c r="F104" t="s">
+        <v>14</v>
+      </c>
+      <c r="G104" t="s">
+        <v>15</v>
+      </c>
+      <c r="H104" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B105" t="s">
         <v>10</v>
@@ -3425,13 +3375,19 @@
       <c r="E105" t="s">
         <v>19</v>
       </c>
-      <c r="H105" s="2" t="b">
-        <v>0</v>
+      <c r="F105" t="s">
+        <v>14</v>
+      </c>
+      <c r="G105" t="s">
+        <v>15</v>
+      </c>
+      <c r="H105" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B106" t="s">
         <v>10</v>
@@ -3445,13 +3401,19 @@
       <c r="E106" t="s">
         <v>13</v>
       </c>
-      <c r="H106" s="2" t="b">
-        <v>0</v>
+      <c r="F106" t="s">
+        <v>14</v>
+      </c>
+      <c r="G106" t="s">
+        <v>15</v>
+      </c>
+      <c r="H106" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B107" t="s">
         <v>10</v>
@@ -3465,13 +3427,19 @@
       <c r="E107" t="s">
         <v>16</v>
       </c>
-      <c r="H107" s="2" t="b">
-        <v>0</v>
+      <c r="F107" t="s">
+        <v>14</v>
+      </c>
+      <c r="G107" t="s">
+        <v>15</v>
+      </c>
+      <c r="H107" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B108" t="s">
         <v>10</v>
@@ -3485,13 +3453,19 @@
       <c r="E108" t="s">
         <v>18</v>
       </c>
-      <c r="H108" s="2" t="b">
-        <v>0</v>
+      <c r="F108" t="s">
+        <v>14</v>
+      </c>
+      <c r="G108" t="s">
+        <v>15</v>
+      </c>
+      <c r="H108" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B109" t="s">
         <v>10</v>
@@ -3505,13 +3479,19 @@
       <c r="E109" t="s">
         <v>19</v>
       </c>
-      <c r="H109" s="2" t="b">
-        <v>0</v>
+      <c r="F109" t="s">
+        <v>14</v>
+      </c>
+      <c r="G109" t="s">
+        <v>15</v>
+      </c>
+      <c r="H109" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B110" t="s">
         <v>10</v>
@@ -3520,21 +3500,24 @@
         <v>11</v>
       </c>
       <c r="D110" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E110" t="s">
         <v>16</v>
       </c>
       <c r="F110" t="s">
+        <v>21</v>
+      </c>
+      <c r="G110" t="s">
         <v>22</v>
       </c>
-      <c r="H110" s="2" t="b">
-        <v>0</v>
+      <c r="H110" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B111" t="s">
         <v>10</v>
@@ -3543,21 +3526,24 @@
         <v>11</v>
       </c>
       <c r="D111" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E111" t="s">
         <v>19</v>
       </c>
       <c r="F111" t="s">
+        <v>21</v>
+      </c>
+      <c r="G111" t="s">
         <v>22</v>
       </c>
-      <c r="H111" s="2" t="b">
-        <v>0</v>
+      <c r="H111" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B112" t="s">
         <v>10</v>
@@ -3566,21 +3552,24 @@
         <v>11</v>
       </c>
       <c r="D112" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E112" t="s">
         <v>16</v>
       </c>
       <c r="F112" t="s">
-        <v>22</v>
-      </c>
-      <c r="H112" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G112" t="s">
+        <v>15</v>
+      </c>
+      <c r="H112" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B113" t="s">
         <v>10</v>
@@ -3589,21 +3578,24 @@
         <v>11</v>
       </c>
       <c r="D113" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E113" t="s">
         <v>19</v>
       </c>
       <c r="F113" t="s">
-        <v>22</v>
-      </c>
-      <c r="H113" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G113" t="s">
+        <v>15</v>
+      </c>
+      <c r="H113" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B114" t="s">
         <v>10</v>
@@ -3612,21 +3604,24 @@
         <v>11</v>
       </c>
       <c r="D114" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E114" t="s">
         <v>16</v>
       </c>
       <c r="F114" t="s">
-        <v>22</v>
-      </c>
-      <c r="H114" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G114" t="s">
+        <v>15</v>
+      </c>
+      <c r="H114" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B115" t="s">
         <v>10</v>
@@ -3635,21 +3630,24 @@
         <v>11</v>
       </c>
       <c r="D115" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E115" t="s">
         <v>19</v>
       </c>
       <c r="F115" t="s">
-        <v>22</v>
-      </c>
-      <c r="H115" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G115" t="s">
+        <v>15</v>
+      </c>
+      <c r="H115" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B116" t="s">
         <v>10</v>
@@ -3658,21 +3656,24 @@
         <v>11</v>
       </c>
       <c r="D116" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E116" t="s">
         <v>13</v>
       </c>
       <c r="F116" t="s">
-        <v>22</v>
-      </c>
-      <c r="H116" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G116" t="s">
+        <v>15</v>
+      </c>
+      <c r="H116" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B117" t="s">
         <v>10</v>
@@ -3681,21 +3682,24 @@
         <v>11</v>
       </c>
       <c r="D117" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E117" t="s">
         <v>16</v>
       </c>
       <c r="F117" t="s">
-        <v>22</v>
-      </c>
-      <c r="H117" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G117" t="s">
+        <v>15</v>
+      </c>
+      <c r="H117" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B118" t="s">
         <v>10</v>
@@ -3704,27 +3708,30 @@
         <v>11</v>
       </c>
       <c r="D118" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E118" t="s">
         <v>19</v>
       </c>
       <c r="F118" t="s">
-        <v>22</v>
-      </c>
-      <c r="H118" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G118" t="s">
+        <v>15</v>
+      </c>
+      <c r="H118" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B119" t="s">
         <v>10</v>
       </c>
       <c r="C119" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D119" t="s">
         <v>12</v>
@@ -3733,21 +3740,24 @@
         <v>16</v>
       </c>
       <c r="F119" t="s">
-        <v>22</v>
-      </c>
-      <c r="H119" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G119" t="s">
+        <v>15</v>
+      </c>
+      <c r="H119" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B120" t="s">
         <v>10</v>
       </c>
       <c r="C120" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D120" t="s">
         <v>12</v>
@@ -3756,21 +3766,24 @@
         <v>19</v>
       </c>
       <c r="F120" t="s">
-        <v>22</v>
-      </c>
-      <c r="H120" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G120" t="s">
+        <v>15</v>
+      </c>
+      <c r="H120" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B121" t="s">
         <v>10</v>
       </c>
       <c r="C121" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D121" t="s">
         <v>20</v>
@@ -3779,21 +3792,24 @@
         <v>16</v>
       </c>
       <c r="F121" t="s">
-        <v>22</v>
-      </c>
-      <c r="H121" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G121" t="s">
+        <v>15</v>
+      </c>
+      <c r="H121" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B122" t="s">
         <v>10</v>
       </c>
       <c r="C122" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D122" t="s">
         <v>20</v>
@@ -3802,107 +3818,122 @@
         <v>19</v>
       </c>
       <c r="F122" t="s">
-        <v>22</v>
-      </c>
-      <c r="H122" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G122" t="s">
+        <v>15</v>
+      </c>
+      <c r="H122" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B123" t="s">
         <v>10</v>
       </c>
       <c r="C123" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D123" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E123" t="s">
         <v>16</v>
       </c>
       <c r="F123" t="s">
-        <v>22</v>
-      </c>
-      <c r="H123" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G123" t="s">
+        <v>15</v>
+      </c>
+      <c r="H123" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B124" t="s">
         <v>10</v>
       </c>
       <c r="C124" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D124" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E124" t="s">
         <v>19</v>
       </c>
       <c r="F124" t="s">
-        <v>22</v>
-      </c>
-      <c r="H124" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G124" t="s">
+        <v>15</v>
+      </c>
+      <c r="H124" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B125" t="s">
         <v>10</v>
       </c>
       <c r="C125" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D125" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E125" t="s">
         <v>16</v>
       </c>
       <c r="F125" t="s">
-        <v>22</v>
-      </c>
-      <c r="H125" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G125" t="s">
+        <v>15</v>
+      </c>
+      <c r="H125" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B126" t="s">
         <v>10</v>
       </c>
       <c r="C126" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D126" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E126" t="s">
         <v>19</v>
       </c>
       <c r="F126" t="s">
-        <v>22</v>
-      </c>
-      <c r="H126" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G126" t="s">
+        <v>15</v>
+      </c>
+      <c r="H126" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B127" t="s">
         <v>10</v>
@@ -3916,13 +3947,19 @@
       <c r="E127" t="s">
         <v>13</v>
       </c>
-      <c r="H127" s="2" t="b">
-        <v>0</v>
+      <c r="F127" t="s">
+        <v>14</v>
+      </c>
+      <c r="G127" t="s">
+        <v>15</v>
+      </c>
+      <c r="H127" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B128" t="s">
         <v>10</v>
@@ -3936,13 +3973,19 @@
       <c r="E128" t="s">
         <v>16</v>
       </c>
-      <c r="H128" s="2" t="b">
-        <v>0</v>
+      <c r="F128" t="s">
+        <v>14</v>
+      </c>
+      <c r="G128" t="s">
+        <v>15</v>
+      </c>
+      <c r="H128" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B129" t="s">
         <v>10</v>
@@ -3956,13 +3999,19 @@
       <c r="E129" t="s">
         <v>18</v>
       </c>
-      <c r="H129" s="2" t="b">
-        <v>0</v>
+      <c r="F129" t="s">
+        <v>14</v>
+      </c>
+      <c r="G129" t="s">
+        <v>17</v>
+      </c>
+      <c r="H129" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B130" t="s">
         <v>10</v>
@@ -3976,13 +4025,19 @@
       <c r="E130" t="s">
         <v>19</v>
       </c>
-      <c r="H130" s="2" t="b">
-        <v>0</v>
+      <c r="F130" t="s">
+        <v>14</v>
+      </c>
+      <c r="G130" t="s">
+        <v>15</v>
+      </c>
+      <c r="H130" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B131" t="s">
         <v>10</v>
@@ -3996,13 +4051,19 @@
       <c r="E131" t="s">
         <v>13</v>
       </c>
-      <c r="H131" s="2" t="b">
-        <v>0</v>
+      <c r="F131" t="s">
+        <v>14</v>
+      </c>
+      <c r="G131" t="s">
+        <v>15</v>
+      </c>
+      <c r="H131" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B132" t="s">
         <v>10</v>
@@ -4016,13 +4077,19 @@
       <c r="E132" t="s">
         <v>16</v>
       </c>
-      <c r="H132" s="2" t="b">
-        <v>0</v>
+      <c r="F132" t="s">
+        <v>14</v>
+      </c>
+      <c r="G132" t="s">
+        <v>15</v>
+      </c>
+      <c r="H132" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B133" t="s">
         <v>10</v>
@@ -4036,13 +4103,19 @@
       <c r="E133" t="s">
         <v>18</v>
       </c>
-      <c r="H133" s="2" t="b">
-        <v>0</v>
+      <c r="F133" t="s">
+        <v>14</v>
+      </c>
+      <c r="G133" t="s">
+        <v>17</v>
+      </c>
+      <c r="H133" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B134" t="s">
         <v>10</v>
@@ -4056,13 +4129,19 @@
       <c r="E134" t="s">
         <v>19</v>
       </c>
-      <c r="H134" s="2" t="b">
-        <v>0</v>
+      <c r="F134" t="s">
+        <v>14</v>
+      </c>
+      <c r="G134" t="s">
+        <v>15</v>
+      </c>
+      <c r="H134" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B135" t="s">
         <v>10</v>
@@ -4071,21 +4150,24 @@
         <v>11</v>
       </c>
       <c r="D135" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E135" t="s">
         <v>16</v>
       </c>
       <c r="F135" t="s">
+        <v>21</v>
+      </c>
+      <c r="G135" t="s">
         <v>22</v>
       </c>
-      <c r="H135" s="2" t="b">
-        <v>0</v>
+      <c r="H135" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B136" t="s">
         <v>10</v>
@@ -4094,21 +4176,24 @@
         <v>11</v>
       </c>
       <c r="D136" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E136" t="s">
         <v>19</v>
       </c>
       <c r="F136" t="s">
+        <v>21</v>
+      </c>
+      <c r="G136" t="s">
         <v>22</v>
       </c>
-      <c r="H136" s="2" t="b">
-        <v>0</v>
+      <c r="H136" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B137" t="s">
         <v>10</v>
@@ -4117,21 +4202,24 @@
         <v>11</v>
       </c>
       <c r="D137" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E137" t="s">
         <v>16</v>
       </c>
       <c r="F137" t="s">
-        <v>22</v>
-      </c>
-      <c r="H137" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G137" t="s">
+        <v>15</v>
+      </c>
+      <c r="H137" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B138" t="s">
         <v>10</v>
@@ -4140,21 +4228,24 @@
         <v>11</v>
       </c>
       <c r="D138" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E138" t="s">
         <v>19</v>
       </c>
       <c r="F138" t="s">
-        <v>22</v>
-      </c>
-      <c r="H138" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G138" t="s">
+        <v>15</v>
+      </c>
+      <c r="H138" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B139" t="s">
         <v>10</v>
@@ -4163,21 +4254,24 @@
         <v>11</v>
       </c>
       <c r="D139" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E139" t="s">
         <v>16</v>
       </c>
       <c r="F139" t="s">
-        <v>22</v>
-      </c>
-      <c r="H139" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G139" t="s">
+        <v>15</v>
+      </c>
+      <c r="H139" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B140" t="s">
         <v>10</v>
@@ -4186,21 +4280,24 @@
         <v>11</v>
       </c>
       <c r="D140" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E140" t="s">
         <v>19</v>
       </c>
       <c r="F140" t="s">
-        <v>22</v>
-      </c>
-      <c r="H140" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G140" t="s">
+        <v>15</v>
+      </c>
+      <c r="H140" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B141" t="s">
         <v>10</v>
@@ -4209,21 +4306,24 @@
         <v>11</v>
       </c>
       <c r="D141" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E141" t="s">
         <v>13</v>
       </c>
       <c r="F141" t="s">
-        <v>22</v>
-      </c>
-      <c r="H141" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G141" t="s">
+        <v>15</v>
+      </c>
+      <c r="H141" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B142" t="s">
         <v>10</v>
@@ -4232,21 +4332,24 @@
         <v>11</v>
       </c>
       <c r="D142" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E142" t="s">
         <v>16</v>
       </c>
       <c r="F142" t="s">
-        <v>22</v>
-      </c>
-      <c r="H142" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G142" t="s">
+        <v>15</v>
+      </c>
+      <c r="H142" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B143" t="s">
         <v>10</v>
@@ -4255,27 +4358,30 @@
         <v>11</v>
       </c>
       <c r="D143" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E143" t="s">
         <v>19</v>
       </c>
       <c r="F143" t="s">
-        <v>22</v>
-      </c>
-      <c r="H143" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G143" t="s">
+        <v>15</v>
+      </c>
+      <c r="H143" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B144" t="s">
         <v>10</v>
       </c>
       <c r="C144" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D144" t="s">
         <v>12</v>
@@ -4284,21 +4390,24 @@
         <v>16</v>
       </c>
       <c r="F144" t="s">
-        <v>22</v>
-      </c>
-      <c r="H144" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G144" t="s">
+        <v>15</v>
+      </c>
+      <c r="H144" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B145" t="s">
         <v>10</v>
       </c>
       <c r="C145" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D145" t="s">
         <v>12</v>
@@ -4307,21 +4416,24 @@
         <v>19</v>
       </c>
       <c r="F145" t="s">
-        <v>22</v>
-      </c>
-      <c r="H145" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G145" t="s">
+        <v>15</v>
+      </c>
+      <c r="H145" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B146" t="s">
         <v>10</v>
       </c>
       <c r="C146" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D146" t="s">
         <v>20</v>
@@ -4330,21 +4442,24 @@
         <v>16</v>
       </c>
       <c r="F146" t="s">
-        <v>22</v>
-      </c>
-      <c r="H146" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G146" t="s">
+        <v>15</v>
+      </c>
+      <c r="H146" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B147" t="s">
         <v>10</v>
       </c>
       <c r="C147" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D147" t="s">
         <v>20</v>
@@ -4353,107 +4468,122 @@
         <v>19</v>
       </c>
       <c r="F147" t="s">
-        <v>22</v>
-      </c>
-      <c r="H147" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G147" t="s">
+        <v>15</v>
+      </c>
+      <c r="H147" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B148" t="s">
         <v>10</v>
       </c>
       <c r="C148" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D148" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E148" t="s">
         <v>16</v>
       </c>
       <c r="F148" t="s">
-        <v>22</v>
-      </c>
-      <c r="H148" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G148" t="s">
+        <v>15</v>
+      </c>
+      <c r="H148" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B149" t="s">
         <v>10</v>
       </c>
       <c r="C149" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D149" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E149" t="s">
         <v>19</v>
       </c>
       <c r="F149" t="s">
-        <v>22</v>
-      </c>
-      <c r="H149" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G149" t="s">
+        <v>15</v>
+      </c>
+      <c r="H149" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B150" t="s">
         <v>10</v>
       </c>
       <c r="C150" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D150" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E150" t="s">
         <v>16</v>
       </c>
       <c r="F150" t="s">
-        <v>22</v>
-      </c>
-      <c r="H150" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G150" t="s">
+        <v>15</v>
+      </c>
+      <c r="H150" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B151" t="s">
         <v>10</v>
       </c>
       <c r="C151" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D151" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E151" t="s">
         <v>19</v>
       </c>
       <c r="F151" t="s">
-        <v>22</v>
-      </c>
-      <c r="H151" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G151" t="s">
+        <v>15</v>
+      </c>
+      <c r="H151" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B152" t="s">
         <v>10</v>
@@ -4467,13 +4597,19 @@
       <c r="E152" t="s">
         <v>13</v>
       </c>
-      <c r="H152" s="2" t="b">
-        <v>0</v>
+      <c r="F152" t="s">
+        <v>14</v>
+      </c>
+      <c r="G152" t="s">
+        <v>15</v>
+      </c>
+      <c r="H152" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B153" t="s">
         <v>10</v>
@@ -4487,13 +4623,19 @@
       <c r="E153" t="s">
         <v>16</v>
       </c>
-      <c r="H153" s="2" t="b">
-        <v>0</v>
+      <c r="F153" t="s">
+        <v>14</v>
+      </c>
+      <c r="G153" t="s">
+        <v>15</v>
+      </c>
+      <c r="H153" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B154" t="s">
         <v>10</v>
@@ -4507,13 +4649,19 @@
       <c r="E154" t="s">
         <v>18</v>
       </c>
-      <c r="H154" s="2" t="b">
-        <v>0</v>
+      <c r="F154" t="s">
+        <v>14</v>
+      </c>
+      <c r="G154" t="s">
+        <v>15</v>
+      </c>
+      <c r="H154" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B155" t="s">
         <v>10</v>
@@ -4527,13 +4675,19 @@
       <c r="E155" t="s">
         <v>19</v>
       </c>
-      <c r="H155" s="2" t="b">
-        <v>0</v>
+      <c r="F155" t="s">
+        <v>14</v>
+      </c>
+      <c r="G155" t="s">
+        <v>15</v>
+      </c>
+      <c r="H155" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B156" t="s">
         <v>10</v>
@@ -4547,13 +4701,19 @@
       <c r="E156" t="s">
         <v>13</v>
       </c>
-      <c r="H156" s="2" t="b">
-        <v>0</v>
+      <c r="F156" t="s">
+        <v>14</v>
+      </c>
+      <c r="G156" t="s">
+        <v>15</v>
+      </c>
+      <c r="H156" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B157" t="s">
         <v>10</v>
@@ -4567,13 +4727,19 @@
       <c r="E157" t="s">
         <v>16</v>
       </c>
-      <c r="H157" s="2" t="b">
-        <v>0</v>
+      <c r="F157" t="s">
+        <v>14</v>
+      </c>
+      <c r="G157" t="s">
+        <v>15</v>
+      </c>
+      <c r="H157" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B158" t="s">
         <v>10</v>
@@ -4587,13 +4753,19 @@
       <c r="E158" t="s">
         <v>18</v>
       </c>
-      <c r="H158" s="2" t="b">
-        <v>0</v>
+      <c r="F158" t="s">
+        <v>14</v>
+      </c>
+      <c r="G158" t="s">
+        <v>15</v>
+      </c>
+      <c r="H158" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B159" t="s">
         <v>10</v>
@@ -4607,13 +4779,19 @@
       <c r="E159" t="s">
         <v>19</v>
       </c>
-      <c r="H159" s="2" t="b">
-        <v>0</v>
+      <c r="F159" t="s">
+        <v>14</v>
+      </c>
+      <c r="G159" t="s">
+        <v>15</v>
+      </c>
+      <c r="H159" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B160" t="s">
         <v>10</v>
@@ -4622,21 +4800,24 @@
         <v>11</v>
       </c>
       <c r="D160" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E160" t="s">
         <v>16</v>
       </c>
       <c r="F160" t="s">
+        <v>21</v>
+      </c>
+      <c r="G160" t="s">
         <v>22</v>
       </c>
-      <c r="H160" s="2" t="b">
-        <v>0</v>
+      <c r="H160" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B161" t="s">
         <v>10</v>
@@ -4645,21 +4826,24 @@
         <v>11</v>
       </c>
       <c r="D161" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E161" t="s">
         <v>19</v>
       </c>
       <c r="F161" t="s">
+        <v>21</v>
+      </c>
+      <c r="G161" t="s">
         <v>22</v>
       </c>
-      <c r="H161" s="2" t="b">
-        <v>0</v>
+      <c r="H161" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B162" t="s">
         <v>10</v>
@@ -4668,21 +4852,24 @@
         <v>11</v>
       </c>
       <c r="D162" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E162" t="s">
         <v>16</v>
       </c>
       <c r="F162" t="s">
-        <v>22</v>
-      </c>
-      <c r="H162" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G162" t="s">
+        <v>15</v>
+      </c>
+      <c r="H162" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B163" t="s">
         <v>10</v>
@@ -4691,21 +4878,24 @@
         <v>11</v>
       </c>
       <c r="D163" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E163" t="s">
         <v>19</v>
       </c>
       <c r="F163" t="s">
-        <v>22</v>
-      </c>
-      <c r="H163" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G163" t="s">
+        <v>15</v>
+      </c>
+      <c r="H163" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B164" t="s">
         <v>10</v>
@@ -4714,21 +4904,24 @@
         <v>11</v>
       </c>
       <c r="D164" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E164" t="s">
         <v>16</v>
       </c>
       <c r="F164" t="s">
-        <v>22</v>
-      </c>
-      <c r="H164" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G164" t="s">
+        <v>15</v>
+      </c>
+      <c r="H164" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B165" t="s">
         <v>10</v>
@@ -4737,21 +4930,24 @@
         <v>11</v>
       </c>
       <c r="D165" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E165" t="s">
         <v>19</v>
       </c>
       <c r="F165" t="s">
-        <v>22</v>
-      </c>
-      <c r="H165" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G165" t="s">
+        <v>15</v>
+      </c>
+      <c r="H165" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B166" t="s">
         <v>10</v>
@@ -4760,21 +4956,24 @@
         <v>11</v>
       </c>
       <c r="D166" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E166" t="s">
         <v>13</v>
       </c>
       <c r="F166" t="s">
-        <v>22</v>
-      </c>
-      <c r="H166" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G166" t="s">
+        <v>15</v>
+      </c>
+      <c r="H166" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B167" t="s">
         <v>10</v>
@@ -4783,21 +4982,24 @@
         <v>11</v>
       </c>
       <c r="D167" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E167" t="s">
         <v>16</v>
       </c>
       <c r="F167" t="s">
-        <v>22</v>
-      </c>
-      <c r="H167" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G167" t="s">
+        <v>15</v>
+      </c>
+      <c r="H167" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B168" t="s">
         <v>10</v>
@@ -4806,27 +5008,30 @@
         <v>11</v>
       </c>
       <c r="D168" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E168" t="s">
         <v>19</v>
       </c>
       <c r="F168" t="s">
-        <v>22</v>
-      </c>
-      <c r="H168" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G168" t="s">
+        <v>15</v>
+      </c>
+      <c r="H168" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B169" t="s">
         <v>10</v>
       </c>
       <c r="C169" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D169" t="s">
         <v>12</v>
@@ -4835,21 +5040,24 @@
         <v>16</v>
       </c>
       <c r="F169" t="s">
-        <v>22</v>
-      </c>
-      <c r="H169" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G169" t="s">
+        <v>15</v>
+      </c>
+      <c r="H169" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B170" t="s">
         <v>10</v>
       </c>
       <c r="C170" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D170" t="s">
         <v>12</v>
@@ -4858,21 +5066,24 @@
         <v>19</v>
       </c>
       <c r="F170" t="s">
-        <v>22</v>
-      </c>
-      <c r="H170" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G170" t="s">
+        <v>15</v>
+      </c>
+      <c r="H170" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B171" t="s">
         <v>10</v>
       </c>
       <c r="C171" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D171" t="s">
         <v>20</v>
@@ -4881,21 +5092,24 @@
         <v>16</v>
       </c>
       <c r="F171" t="s">
-        <v>22</v>
-      </c>
-      <c r="H171" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G171" t="s">
+        <v>15</v>
+      </c>
+      <c r="H171" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B172" t="s">
         <v>10</v>
       </c>
       <c r="C172" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D172" t="s">
         <v>20</v>
@@ -4904,110 +5118,125 @@
         <v>19</v>
       </c>
       <c r="F172" t="s">
-        <v>22</v>
-      </c>
-      <c r="H172" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G172" t="s">
+        <v>15</v>
+      </c>
+      <c r="H172" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B173" t="s">
         <v>10</v>
       </c>
       <c r="C173" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D173" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E173" t="s">
         <v>16</v>
       </c>
       <c r="F173" t="s">
-        <v>22</v>
-      </c>
-      <c r="H173" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G173" t="s">
+        <v>15</v>
+      </c>
+      <c r="H173" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B174" t="s">
         <v>10</v>
       </c>
       <c r="C174" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D174" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E174" t="s">
         <v>19</v>
       </c>
       <c r="F174" t="s">
-        <v>22</v>
-      </c>
-      <c r="H174" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G174" t="s">
+        <v>15</v>
+      </c>
+      <c r="H174" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B175" t="s">
         <v>10</v>
       </c>
       <c r="C175" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D175" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E175" t="s">
         <v>16</v>
       </c>
       <c r="F175" t="s">
-        <v>22</v>
-      </c>
-      <c r="H175" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G175" t="s">
+        <v>15</v>
+      </c>
+      <c r="H175" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B176" t="s">
         <v>10</v>
       </c>
       <c r="C176" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D176" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E176" t="s">
         <v>19</v>
       </c>
       <c r="F176" t="s">
-        <v>22</v>
-      </c>
-      <c r="H176" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G176" t="s">
+        <v>15</v>
+      </c>
+      <c r="H176" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>39</v>
+      </c>
+      <c r="B177" t="s">
         <v>40</v>
-      </c>
-      <c r="B177" t="s">
-        <v>41</v>
       </c>
       <c r="C177" t="s">
         <v>11</v>
@@ -5018,16 +5247,22 @@
       <c r="E177" t="s">
         <v>13</v>
       </c>
-      <c r="H177" s="2" t="b">
-        <v>0</v>
+      <c r="F177" t="s">
+        <v>42</v>
+      </c>
+      <c r="G177" t="s">
+        <v>43</v>
+      </c>
+      <c r="H177" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>39</v>
+      </c>
+      <c r="B178" t="s">
         <v>40</v>
-      </c>
-      <c r="B178" t="s">
-        <v>41</v>
       </c>
       <c r="C178" t="s">
         <v>11</v>
@@ -5038,16 +5273,22 @@
       <c r="E178" t="s">
         <v>16</v>
       </c>
-      <c r="H178" s="2" t="b">
-        <v>0</v>
+      <c r="F178" t="s">
+        <v>42</v>
+      </c>
+      <c r="G178" t="s">
+        <v>43</v>
+      </c>
+      <c r="H178" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>39</v>
+      </c>
+      <c r="B179" t="s">
         <v>40</v>
-      </c>
-      <c r="B179" t="s">
-        <v>41</v>
       </c>
       <c r="C179" t="s">
         <v>11</v>
@@ -5058,16 +5299,22 @@
       <c r="E179" t="s">
         <v>18</v>
       </c>
-      <c r="H179" s="2" t="b">
-        <v>0</v>
+      <c r="F179" t="s">
+        <v>42</v>
+      </c>
+      <c r="G179" t="s">
+        <v>43</v>
+      </c>
+      <c r="H179" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>39</v>
+      </c>
+      <c r="B180" t="s">
         <v>40</v>
-      </c>
-      <c r="B180" t="s">
-        <v>41</v>
       </c>
       <c r="C180" t="s">
         <v>11</v>
@@ -5078,16 +5325,22 @@
       <c r="E180" t="s">
         <v>19</v>
       </c>
-      <c r="H180" s="2" t="b">
-        <v>0</v>
+      <c r="F180" t="s">
+        <v>42</v>
+      </c>
+      <c r="G180" t="s">
+        <v>43</v>
+      </c>
+      <c r="H180" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>39</v>
+      </c>
+      <c r="B181" t="s">
         <v>40</v>
-      </c>
-      <c r="B181" t="s">
-        <v>41</v>
       </c>
       <c r="C181" t="s">
         <v>11</v>
@@ -5098,16 +5351,22 @@
       <c r="E181" t="s">
         <v>13</v>
       </c>
-      <c r="H181" s="2" t="b">
-        <v>0</v>
+      <c r="F181" t="s">
+        <v>42</v>
+      </c>
+      <c r="G181" t="s">
+        <v>43</v>
+      </c>
+      <c r="H181" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
+        <v>39</v>
+      </c>
+      <c r="B182" t="s">
         <v>40</v>
-      </c>
-      <c r="B182" t="s">
-        <v>41</v>
       </c>
       <c r="C182" t="s">
         <v>11</v>
@@ -5118,16 +5377,22 @@
       <c r="E182" t="s">
         <v>16</v>
       </c>
-      <c r="H182" s="2" t="b">
-        <v>0</v>
+      <c r="F182" t="s">
+        <v>42</v>
+      </c>
+      <c r="G182" t="s">
+        <v>43</v>
+      </c>
+      <c r="H182" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>39</v>
+      </c>
+      <c r="B183" t="s">
         <v>40</v>
-      </c>
-      <c r="B183" t="s">
-        <v>41</v>
       </c>
       <c r="C183" t="s">
         <v>11</v>
@@ -5138,16 +5403,22 @@
       <c r="E183" t="s">
         <v>18</v>
       </c>
-      <c r="H183" s="2" t="b">
-        <v>0</v>
+      <c r="F183" t="s">
+        <v>42</v>
+      </c>
+      <c r="G183" t="s">
+        <v>43</v>
+      </c>
+      <c r="H183" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
+        <v>39</v>
+      </c>
+      <c r="B184" t="s">
         <v>40</v>
-      </c>
-      <c r="B184" t="s">
-        <v>41</v>
       </c>
       <c r="C184" t="s">
         <v>11</v>
@@ -5158,226 +5429,259 @@
       <c r="E184" t="s">
         <v>19</v>
       </c>
-      <c r="H184" s="2" t="b">
-        <v>0</v>
+      <c r="F184" t="s">
+        <v>42</v>
+      </c>
+      <c r="G184" t="s">
+        <v>43</v>
+      </c>
+      <c r="H184" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
+        <v>39</v>
+      </c>
+      <c r="B185" t="s">
         <v>40</v>
       </c>
-      <c r="B185" t="s">
+      <c r="C185" t="s">
+        <v>11</v>
+      </c>
+      <c r="D185" t="s">
         <v>41</v>
       </c>
-      <c r="C185" t="s">
-        <v>11</v>
-      </c>
-      <c r="D185" t="s">
-        <v>21</v>
-      </c>
       <c r="E185" t="s">
         <v>16</v>
       </c>
       <c r="F185" t="s">
-        <v>22</v>
-      </c>
-      <c r="H185" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G185" t="s">
+        <v>43</v>
+      </c>
+      <c r="H185" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
+        <v>39</v>
+      </c>
+      <c r="B186" t="s">
         <v>40</v>
       </c>
-      <c r="B186" t="s">
+      <c r="C186" t="s">
+        <v>11</v>
+      </c>
+      <c r="D186" t="s">
         <v>41</v>
       </c>
-      <c r="C186" t="s">
-        <v>11</v>
-      </c>
-      <c r="D186" t="s">
-        <v>21</v>
-      </c>
       <c r="E186" t="s">
         <v>19</v>
       </c>
       <c r="F186" t="s">
-        <v>22</v>
-      </c>
-      <c r="H186" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G186" t="s">
+        <v>43</v>
+      </c>
+      <c r="H186" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
+        <v>39</v>
+      </c>
+      <c r="B187" t="s">
         <v>40</v>
       </c>
-      <c r="B187" t="s">
-        <v>41</v>
-      </c>
       <c r="C187" t="s">
         <v>11</v>
       </c>
       <c r="D187" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E187" t="s">
         <v>16</v>
       </c>
       <c r="F187" t="s">
-        <v>22</v>
-      </c>
-      <c r="H187" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G187" t="s">
+        <v>43</v>
+      </c>
+      <c r="H187" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
+        <v>39</v>
+      </c>
+      <c r="B188" t="s">
         <v>40</v>
       </c>
-      <c r="B188" t="s">
-        <v>41</v>
-      </c>
       <c r="C188" t="s">
         <v>11</v>
       </c>
       <c r="D188" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E188" t="s">
         <v>19</v>
       </c>
       <c r="F188" t="s">
-        <v>22</v>
-      </c>
-      <c r="H188" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G188" t="s">
+        <v>43</v>
+      </c>
+      <c r="H188" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
+        <v>39</v>
+      </c>
+      <c r="B189" t="s">
         <v>40</v>
       </c>
-      <c r="B189" t="s">
-        <v>41</v>
-      </c>
       <c r="C189" t="s">
         <v>11</v>
       </c>
       <c r="D189" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E189" t="s">
         <v>16</v>
       </c>
       <c r="F189" t="s">
-        <v>22</v>
-      </c>
-      <c r="H189" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G189" t="s">
+        <v>43</v>
+      </c>
+      <c r="H189" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
+        <v>39</v>
+      </c>
+      <c r="B190" t="s">
         <v>40</v>
       </c>
-      <c r="B190" t="s">
-        <v>41</v>
-      </c>
       <c r="C190" t="s">
         <v>11</v>
       </c>
       <c r="D190" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E190" t="s">
         <v>19</v>
       </c>
       <c r="F190" t="s">
-        <v>22</v>
-      </c>
-      <c r="H190" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G190" t="s">
+        <v>43</v>
+      </c>
+      <c r="H190" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
+        <v>39</v>
+      </c>
+      <c r="B191" t="s">
         <v>40</v>
       </c>
-      <c r="B191" t="s">
-        <v>41</v>
-      </c>
       <c r="C191" t="s">
         <v>11</v>
       </c>
       <c r="D191" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E191" t="s">
         <v>13</v>
       </c>
       <c r="F191" t="s">
-        <v>22</v>
-      </c>
-      <c r="H191" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G191" t="s">
+        <v>43</v>
+      </c>
+      <c r="H191" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
+        <v>39</v>
+      </c>
+      <c r="B192" t="s">
         <v>40</v>
       </c>
-      <c r="B192" t="s">
-        <v>41</v>
-      </c>
       <c r="C192" t="s">
         <v>11</v>
       </c>
       <c r="D192" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E192" t="s">
         <v>16</v>
       </c>
       <c r="F192" t="s">
-        <v>22</v>
-      </c>
-      <c r="H192" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G192" t="s">
+        <v>43</v>
+      </c>
+      <c r="H192" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
+        <v>39</v>
+      </c>
+      <c r="B193" t="s">
         <v>40</v>
       </c>
-      <c r="B193" t="s">
-        <v>41</v>
-      </c>
       <c r="C193" t="s">
         <v>11</v>
       </c>
       <c r="D193" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E193" t="s">
         <v>19</v>
       </c>
       <c r="F193" t="s">
-        <v>22</v>
-      </c>
-      <c r="H193" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G193" t="s">
+        <v>43</v>
+      </c>
+      <c r="H193" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
+        <v>39</v>
+      </c>
+      <c r="B194" t="s">
         <v>40</v>
       </c>
-      <c r="B194" t="s">
-        <v>41</v>
-      </c>
       <c r="C194" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D194" t="s">
         <v>12</v>
@@ -5386,21 +5690,24 @@
         <v>16</v>
       </c>
       <c r="F194" t="s">
-        <v>22</v>
-      </c>
-      <c r="H194" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G194" t="s">
+        <v>43</v>
+      </c>
+      <c r="H194" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
+        <v>39</v>
+      </c>
+      <c r="B195" t="s">
         <v>40</v>
       </c>
-      <c r="B195" t="s">
-        <v>41</v>
-      </c>
       <c r="C195" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D195" t="s">
         <v>12</v>
@@ -5409,21 +5716,24 @@
         <v>19</v>
       </c>
       <c r="F195" t="s">
-        <v>22</v>
-      </c>
-      <c r="H195" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G195" t="s">
+        <v>43</v>
+      </c>
+      <c r="H195" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>39</v>
+      </c>
+      <c r="B196" t="s">
         <v>40</v>
       </c>
-      <c r="B196" t="s">
-        <v>41</v>
-      </c>
       <c r="C196" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D196" t="s">
         <v>20</v>
@@ -5432,21 +5742,24 @@
         <v>16</v>
       </c>
       <c r="F196" t="s">
-        <v>22</v>
-      </c>
-      <c r="H196" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G196" t="s">
+        <v>43</v>
+      </c>
+      <c r="H196" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>39</v>
+      </c>
+      <c r="B197" t="s">
         <v>40</v>
       </c>
-      <c r="B197" t="s">
-        <v>41</v>
-      </c>
       <c r="C197" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D197" t="s">
         <v>20</v>
@@ -5455,110 +5768,333 @@
         <v>19</v>
       </c>
       <c r="F197" t="s">
-        <v>22</v>
-      </c>
-      <c r="H197" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G197" t="s">
+        <v>43</v>
+      </c>
+      <c r="H197" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
+        <v>39</v>
+      </c>
+      <c r="B198" t="s">
         <v>40</v>
       </c>
-      <c r="B198" t="s">
-        <v>41</v>
-      </c>
       <c r="C198" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D198" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E198" t="s">
         <v>16</v>
       </c>
       <c r="F198" t="s">
-        <v>22</v>
-      </c>
-      <c r="H198" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G198" t="s">
+        <v>43</v>
+      </c>
+      <c r="H198" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
+        <v>39</v>
+      </c>
+      <c r="B199" t="s">
         <v>40</v>
       </c>
-      <c r="B199" t="s">
-        <v>41</v>
-      </c>
       <c r="C199" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D199" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E199" t="s">
         <v>19</v>
       </c>
       <c r="F199" t="s">
-        <v>22</v>
-      </c>
-      <c r="H199" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G199" t="s">
+        <v>43</v>
+      </c>
+      <c r="H199" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
+        <v>39</v>
+      </c>
+      <c r="B200" t="s">
         <v>40</v>
       </c>
-      <c r="B200" t="s">
-        <v>41</v>
-      </c>
       <c r="C200" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D200" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E200" t="s">
         <v>16</v>
       </c>
       <c r="F200" t="s">
-        <v>22</v>
-      </c>
-      <c r="H200" s="2" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G200" t="s">
+        <v>43</v>
+      </c>
+      <c r="H200" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
+        <v>39</v>
+      </c>
+      <c r="B201" t="s">
         <v>40</v>
       </c>
-      <c r="B201" t="s">
-        <v>41</v>
-      </c>
       <c r="C201" t="s">
+        <v>26</v>
+      </c>
+      <c r="D201" t="s">
+        <v>25</v>
+      </c>
+      <c r="E201" t="s">
+        <v>19</v>
+      </c>
+      <c r="F201" t="s">
+        <v>21</v>
+      </c>
+      <c r="G201" t="s">
+        <v>43</v>
+      </c>
+      <c r="H201" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>9</v>
+      </c>
+      <c r="B202" t="s">
+        <v>10</v>
+      </c>
+      <c r="C202" t="s">
+        <v>11</v>
+      </c>
+      <c r="D202" t="s">
+        <v>24</v>
+      </c>
+      <c r="E202" t="s">
+        <v>13</v>
+      </c>
+      <c r="F202" t="s">
+        <v>21</v>
+      </c>
+      <c r="G202" t="s">
+        <v>15</v>
+      </c>
+      <c r="H202" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>9</v>
+      </c>
+      <c r="B203" t="s">
         <v>27</v>
       </c>
-      <c r="D201" t="s">
-        <v>26</v>
-      </c>
-      <c r="E201" t="s">
-        <v>19</v>
-      </c>
-      <c r="F201" t="s">
-        <v>22</v>
-      </c>
-      <c r="H201" s="2" t="b">
-        <v>0</v>
+      <c r="C203" t="s">
+        <v>11</v>
+      </c>
+      <c r="D203" t="s">
+        <v>24</v>
+      </c>
+      <c r="E203" t="s">
+        <v>13</v>
+      </c>
+      <c r="F203" t="s">
+        <v>21</v>
+      </c>
+      <c r="G203" t="s">
+        <v>29</v>
+      </c>
+      <c r="H203" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>9</v>
+      </c>
+      <c r="B204" t="s">
+        <v>31</v>
+      </c>
+      <c r="C204" t="s">
+        <v>11</v>
+      </c>
+      <c r="D204" t="s">
+        <v>24</v>
+      </c>
+      <c r="E204" t="s">
+        <v>13</v>
+      </c>
+      <c r="F204" t="s">
+        <v>21</v>
+      </c>
+      <c r="G204" t="s">
+        <v>29</v>
+      </c>
+      <c r="H204" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>32</v>
+      </c>
+      <c r="B205" t="s">
+        <v>10</v>
+      </c>
+      <c r="C205" t="s">
+        <v>11</v>
+      </c>
+      <c r="D205" t="s">
+        <v>24</v>
+      </c>
+      <c r="E205" t="s">
+        <v>13</v>
+      </c>
+      <c r="F205" t="s">
+        <v>21</v>
+      </c>
+      <c r="G205" t="s">
+        <v>34</v>
+      </c>
+      <c r="H205" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>36</v>
+      </c>
+      <c r="B206" t="s">
+        <v>10</v>
+      </c>
+      <c r="C206" t="s">
+        <v>11</v>
+      </c>
+      <c r="D206" t="s">
+        <v>24</v>
+      </c>
+      <c r="E206" t="s">
+        <v>13</v>
+      </c>
+      <c r="F206" t="s">
+        <v>21</v>
+      </c>
+      <c r="G206" t="s">
+        <v>15</v>
+      </c>
+      <c r="H206" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>37</v>
+      </c>
+      <c r="B207" t="s">
+        <v>10</v>
+      </c>
+      <c r="C207" t="s">
+        <v>11</v>
+      </c>
+      <c r="D207" t="s">
+        <v>24</v>
+      </c>
+      <c r="E207" t="s">
+        <v>13</v>
+      </c>
+      <c r="F207" t="s">
+        <v>21</v>
+      </c>
+      <c r="G207" t="s">
+        <v>15</v>
+      </c>
+      <c r="H207" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>38</v>
+      </c>
+      <c r="B208" t="s">
+        <v>10</v>
+      </c>
+      <c r="C208" t="s">
+        <v>11</v>
+      </c>
+      <c r="D208" t="s">
+        <v>24</v>
+      </c>
+      <c r="E208" t="s">
+        <v>13</v>
+      </c>
+      <c r="F208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G208" t="s">
+        <v>15</v>
+      </c>
+      <c r="H208" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>39</v>
+      </c>
+      <c r="B209" t="s">
+        <v>40</v>
+      </c>
+      <c r="C209" t="s">
+        <v>11</v>
+      </c>
+      <c r="D209" t="s">
+        <v>24</v>
+      </c>
+      <c r="E209" t="s">
+        <v>13</v>
+      </c>
+      <c r="F209" t="s">
+        <v>21</v>
+      </c>
+      <c r="G209" t="s">
+        <v>43</v>
+      </c>
+      <c r="H209" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G201" xr:uid="{CAD56FC0-C9C7-4DEB-B2BD-3170FBBF9EA0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G209" xr:uid="{CAD56FC0-C9C7-4DEB-B2BD-3170FBBF9EA0}">
       <formula1>R_Buyer_name</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F201" xr:uid="{4AA9782B-E461-4452-A066-5D9D23101967}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F209" xr:uid="{4AA9782B-E461-4452-A066-5D9D23101967}">
       <formula1>R_warehouse_rep_name</formula1>
     </dataValidation>
   </dataValidations>
